--- a/nr-update-system-nss/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
+++ b/nr-update-system-nss/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-22T17:34:51+00:00</t>
+    <t>2026-02-23T07:43:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-system-nss/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
+++ b/nr-update-system-nss/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot-2</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:28:50+00:00</t>
+    <t>2026-03-25T14:42:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0-ballot-2</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -633,7 +633,7 @@
     <t>shortName</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-short-name|2.2.0-ballot-2}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-short-name|2.2.0}
 </t>
   </si>
   <si>
@@ -704,14 +704,14 @@
     <t>member</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-member|2.2.0-ballot-2}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-member|2.2.0}
 </t>
   </si>
   <si>
-    <t>FR Core Organization Extension - Membre d'organisation</t>
-  </si>
-  <si>
-    <t>Extension permettant de définir des membres d'une organisation.</t>
+    <t>FR Core Organization Extension - quelles sont les entités qui font partie de l'organisation</t>
+  </si>
+  <si>
+    <t>Extension permettant de définir des membres d'une organisation. Les membres sont des organisations filles de la ressources. C'est la relation inverse de partOf.</t>
   </si>
   <si>
     <t>Organization.extension:sae</t>
@@ -720,7 +720,7 @@
     <t>sae</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-sae-category|2.2.0-ballot-2}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-sae-categorie|2.2.0}
 </t>
   </si>
   <si>
@@ -736,7 +736,7 @@
     <t>raisonSociale</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-raison-sociale|2.2.0-ballot-2}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-raison-sociale|2.2.0}
 </t>
   </si>
   <si>
@@ -853,7 +853,7 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-organization-identifier-type|2.2.0-ballot-2</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-organization-identifier-type|2.2.0</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1366,7 +1366,7 @@
     <t>rppsRang</t>
   </si>
   <si>
-    <t>RPPS rang (11 chiffres RPPS + 2 chiffres RANG)</t>
+    <t>RPPS rang (11 chiffres RPPS + 2 ou 3 chiffres RANG)</t>
   </si>
   <si>
     <t>Organization.identifier:rppsRang.id</t>
@@ -1384,7 +1384,7 @@
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
     &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
-    &lt;code value="INTRN"/&gt;
+    &lt;code value="RPPSRG"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
@@ -1452,7 +1452,7 @@
     <t>Need to be able to track the kind of organization that this is - different organization types have different uses.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-organization-etablissement-type|2.2.0-ballot-2</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-organization-etablissement-type|2.2.0</t>
   </si>
   <si>
     <t>No equivalent in v2</t>
@@ -1507,7 +1507,7 @@
     <t>Organization.telecom</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0-ballot-2}
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0}
 </t>
   </si>
   <si>
@@ -1543,7 +1543,7 @@
     <t>Organization.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address|2.2.0-ballot-2}
+    <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address|2.2.0}
 </t>
   </si>
   <si>
@@ -1579,7 +1579,7 @@
     <t>Organization.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0-ballot-2|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-etablissement|2.2.0-ballot-2)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-etablissement|2.2.0)
 </t>
   </si>
   <si>
@@ -1633,7 +1633,7 @@
     <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-organization-type|2.2.0-ballot-2</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-organization-type|2.2.0</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -2150,7 +2150,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="145.421875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="132.328125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2165,7 +2165,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="72.578125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="66.03125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -4825,7 +4825,7 @@
         <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>78</v>
